--- a/DB Arcoiris Dashboard.xlsx
+++ b/DB Arcoiris Dashboard.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utilisateur\Desktop\Documents\GitHub\DASHBOARD_BRASIL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Edoardo\.gemini\antigravity\scratch\DASHBOARD_BRASIL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80D575E8-B28E-4C49-B01C-49F8C050805A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF7547FB-D74D-4F49-9DA1-3303265A47DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{4DC6B9C3-1844-4AFD-84C5-8F1E979BB903}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4DC6B9C3-1844-4AFD-84C5-8F1E979BB903}"/>
   </bookViews>
   <sheets>
     <sheet name="DATABASE TOT" sheetId="1" r:id="rId1"/>
@@ -8178,15 +8178,15 @@
       <c r="S116" s="48"/>
       <c r="T116" s="51">
         <f>AVERAGEIF(O110:O121,"&gt;1")</f>
-        <v>1180.2987499999999</v>
+        <v>1169.7666666666667</v>
       </c>
       <c r="U116" s="72">
         <f>(T116-T104)/T104</f>
-        <v>-4.6743190582914394E-2</v>
+        <v>-5.5249325283851881E-2</v>
       </c>
       <c r="W116" s="44">
         <f>AVERAGEIF(Q110:Q121,"&gt;1%")</f>
-        <v>0.45463749999999997</v>
+        <v>0.47296666666666659</v>
       </c>
       <c r="X116" s="5"/>
     </row>
@@ -8268,30 +8268,46 @@
       <c r="E118" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="F118" s="23"/>
-      <c r="G118" s="23"/>
-      <c r="H118" s="23"/>
-      <c r="I118" s="23"/>
+      <c r="F118" s="23">
+        <v>689581.59000000008</v>
+      </c>
+      <c r="G118" s="23">
+        <v>72296</v>
+      </c>
+      <c r="H118" s="23">
+        <v>52365</v>
+      </c>
+      <c r="I118" s="23">
+        <v>0</v>
+      </c>
       <c r="J118" s="24">
         <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="K118" s="23"/>
-      <c r="L118" s="25" t="str">
+        <v>814242.59000000008</v>
+      </c>
+      <c r="K118" s="23">
+        <v>7177.7000000000007</v>
+      </c>
+      <c r="L118" s="25">
         <f t="shared" si="10"/>
-        <v/>
+        <v>8.7381576610434109E-3</v>
       </c>
       <c r="M118" s="24">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>821420.29</v>
       </c>
       <c r="N118" s="49">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="O118" s="23"/>
-      <c r="P118" s="66"/>
-      <c r="Q118" s="62"/>
+        <v>0.89366804768384589</v>
+      </c>
+      <c r="O118" s="23">
+        <v>1085.51</v>
+      </c>
+      <c r="P118" s="66">
+        <v>632</v>
+      </c>
+      <c r="Q118" s="62">
+        <v>0.61960000000000004</v>
+      </c>
       <c r="R118" s="48"/>
       <c r="S118" s="48"/>
       <c r="X118" s="5"/>
@@ -8431,11 +8447,11 @@
       <c r="S121" s="53"/>
       <c r="T121" s="43">
         <f>SUM(M110:M121)</f>
-        <v>5583484.0700000003</v>
+        <v>6404904.3600000003</v>
       </c>
       <c r="U121" s="60">
         <f>(T121-T109)/T109</f>
-        <v>-0.30684347106895438</v>
+        <v>-0.20486899959707053</v>
       </c>
       <c r="V121" s="45">
         <f>V109+1</f>
